--- a/AAII_Financials/Yearly/TOSYY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/TOSYY_YR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Yearly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Yearly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,7 +17,7 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
@@ -724,25 +724,25 @@
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>22321400</v>
+        <v>22657600</v>
       </c>
       <c r="E8" s="3">
-        <v>22157500</v>
+        <v>22491200</v>
       </c>
       <c r="F8" s="3">
-        <v>20281100</v>
+        <v>20586500</v>
       </c>
       <c r="G8" s="3">
-        <v>22508700</v>
+        <v>22847700</v>
       </c>
       <c r="H8" s="3">
-        <v>24525100</v>
+        <v>24894500</v>
       </c>
       <c r="I8" s="3">
-        <v>26212000</v>
+        <v>26606800</v>
       </c>
       <c r="J8" s="3">
-        <v>26850400</v>
+        <v>27254800</v>
       </c>
       <c r="K8" s="3">
         <v>37888100</v>
@@ -766,25 +766,25 @@
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>16412000</v>
+        <v>16659100</v>
       </c>
       <c r="E9" s="3">
-        <v>16266400</v>
+        <v>16511400</v>
       </c>
       <c r="F9" s="3">
-        <v>14791000</v>
+        <v>15013800</v>
       </c>
       <c r="G9" s="3">
-        <v>16388600</v>
+        <v>16635400</v>
       </c>
       <c r="H9" s="3">
-        <v>18439200</v>
+        <v>18716900</v>
       </c>
       <c r="I9" s="3">
-        <v>19738900</v>
+        <v>20036200</v>
       </c>
       <c r="J9" s="3">
-        <v>19791600</v>
+        <v>20089700</v>
       </c>
       <c r="K9" s="3">
         <v>32364400</v>
@@ -808,25 +808,25 @@
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>5909400</v>
+        <v>5998400</v>
       </c>
       <c r="E10" s="3">
-        <v>5891100</v>
+        <v>5979800</v>
       </c>
       <c r="F10" s="3">
-        <v>5490000</v>
+        <v>5572700</v>
       </c>
       <c r="G10" s="3">
-        <v>6120100</v>
+        <v>6212300</v>
       </c>
       <c r="H10" s="3">
-        <v>6085900</v>
+        <v>6177500</v>
       </c>
       <c r="I10" s="3">
-        <v>6473100</v>
+        <v>6570600</v>
       </c>
       <c r="J10" s="3">
-        <v>7058800</v>
+        <v>7165100</v>
       </c>
       <c r="K10" s="3">
         <v>5523600</v>
@@ -952,25 +952,25 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>-63000</v>
+        <v>-63900</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>8</v>
       </c>
       <c r="F14" s="3">
-        <v>21600</v>
+        <v>21900</v>
       </c>
       <c r="G14" s="3">
-        <v>25500</v>
+        <v>25900</v>
       </c>
       <c r="H14" s="3">
-        <v>182200</v>
+        <v>184900</v>
       </c>
       <c r="I14" s="3">
-        <v>93700</v>
+        <v>95100</v>
       </c>
       <c r="J14" s="3">
-        <v>341600</v>
+        <v>346700</v>
       </c>
       <c r="K14" s="3">
         <v>348200</v>
@@ -1051,25 +1051,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>21378300</v>
+        <v>21700200</v>
       </c>
       <c r="E17" s="3">
-        <v>20941900</v>
+        <v>21257300</v>
       </c>
       <c r="F17" s="3">
-        <v>19536200</v>
+        <v>19830400</v>
       </c>
       <c r="G17" s="3">
-        <v>21833200</v>
+        <v>22162000</v>
       </c>
       <c r="H17" s="3">
-        <v>24615100</v>
+        <v>24985800</v>
       </c>
       <c r="I17" s="3">
-        <v>26141800</v>
+        <v>26535500</v>
       </c>
       <c r="J17" s="3">
-        <v>26840900</v>
+        <v>27245100</v>
       </c>
       <c r="K17" s="3">
         <v>41438200</v>
@@ -1093,25 +1093,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>943100</v>
+        <v>957300</v>
       </c>
       <c r="E18" s="3">
-        <v>1215500</v>
+        <v>1233800</v>
       </c>
       <c r="F18" s="3">
-        <v>744900</v>
+        <v>756100</v>
       </c>
       <c r="G18" s="3">
-        <v>675500</v>
+        <v>685700</v>
       </c>
       <c r="H18" s="3">
-        <v>-90000</v>
+        <v>-91400</v>
       </c>
       <c r="I18" s="3">
-        <v>70200</v>
+        <v>71200</v>
       </c>
       <c r="J18" s="3">
-        <v>9500</v>
+        <v>9700</v>
       </c>
       <c r="K18" s="3">
         <v>-3550100</v>
@@ -1153,25 +1153,25 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>343800</v>
+        <v>349000</v>
       </c>
       <c r="E20" s="3">
-        <v>401100</v>
+        <v>407100</v>
       </c>
       <c r="F20" s="3">
-        <v>304500</v>
+        <v>309100</v>
       </c>
       <c r="G20" s="3">
-        <v>-955300</v>
+        <v>-969700</v>
       </c>
       <c r="H20" s="3">
-        <v>232600</v>
+        <v>236100</v>
       </c>
       <c r="I20" s="3">
-        <v>671800</v>
+        <v>681900</v>
       </c>
       <c r="J20" s="3">
-        <v>412000</v>
+        <v>418200</v>
       </c>
       <c r="K20" s="3">
         <v>746200</v>
@@ -1195,25 +1195,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>1917100</v>
+        <v>1951700</v>
       </c>
       <c r="E21" s="3">
-        <v>2179500</v>
+        <v>2217500</v>
       </c>
       <c r="F21" s="3">
-        <v>1612600</v>
+        <v>1642000</v>
       </c>
       <c r="G21" s="3">
-        <v>246500</v>
+        <v>255000</v>
       </c>
       <c r="H21" s="3">
-        <v>661600</v>
+        <v>676300</v>
       </c>
       <c r="I21" s="3">
-        <v>1522400</v>
+        <v>1552500</v>
       </c>
       <c r="J21" s="3">
-        <v>1498800</v>
+        <v>1531200</v>
       </c>
       <c r="K21" s="3">
         <v>-1247000</v>
@@ -1237,25 +1237,25 @@
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>32200</v>
+        <v>32700</v>
       </c>
       <c r="E22" s="3">
-        <v>29000</v>
+        <v>29400</v>
       </c>
       <c r="F22" s="3">
-        <v>30200</v>
+        <v>30700</v>
       </c>
       <c r="G22" s="3">
-        <v>35900</v>
+        <v>36500</v>
       </c>
       <c r="H22" s="3">
-        <v>70100</v>
+        <v>71200</v>
       </c>
       <c r="I22" s="3">
-        <v>195000</v>
+        <v>197900</v>
       </c>
       <c r="J22" s="3">
-        <v>123100</v>
+        <v>125000</v>
       </c>
       <c r="K22" s="3">
         <v>131400</v>
@@ -1279,25 +1279,25 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>1254700</v>
+        <v>1273600</v>
       </c>
       <c r="E23" s="3">
-        <v>1587700</v>
+        <v>1611600</v>
       </c>
       <c r="F23" s="3">
-        <v>1019200</v>
+        <v>1034500</v>
       </c>
       <c r="G23" s="3">
-        <v>-315700</v>
+        <v>-320400</v>
       </c>
       <c r="H23" s="3">
-        <v>72400</v>
+        <v>73500</v>
       </c>
       <c r="I23" s="3">
-        <v>547000</v>
+        <v>555200</v>
       </c>
       <c r="J23" s="3">
-        <v>298400</v>
+        <v>302900</v>
       </c>
       <c r="K23" s="3">
         <v>-2935300</v>
@@ -1321,25 +1321,25 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>424800</v>
+        <v>431200</v>
       </c>
       <c r="E24" s="3">
-        <v>165000</v>
+        <v>167500</v>
       </c>
       <c r="F24" s="3">
-        <v>91400</v>
+        <v>92700</v>
       </c>
       <c r="G24" s="3">
-        <v>233200</v>
+        <v>236700</v>
       </c>
       <c r="H24" s="3">
-        <v>103300</v>
+        <v>104800</v>
       </c>
       <c r="I24" s="3">
-        <v>-411300</v>
+        <v>-417500</v>
       </c>
       <c r="J24" s="3">
-        <v>384900</v>
+        <v>390700</v>
       </c>
       <c r="K24" s="3">
         <v>1811100</v>
@@ -1405,25 +1405,25 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>829900</v>
+        <v>842400</v>
       </c>
       <c r="E26" s="3">
-        <v>1422700</v>
+        <v>1444100</v>
       </c>
       <c r="F26" s="3">
-        <v>927800</v>
+        <v>941800</v>
       </c>
       <c r="G26" s="3">
-        <v>-548900</v>
+        <v>-557100</v>
       </c>
       <c r="H26" s="3">
-        <v>-30800</v>
+        <v>-31300</v>
       </c>
       <c r="I26" s="3">
-        <v>958300</v>
+        <v>972700</v>
       </c>
       <c r="J26" s="3">
-        <v>-86500</v>
+        <v>-87800</v>
       </c>
       <c r="K26" s="3">
         <v>-4746400</v>
@@ -1447,25 +1447,25 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>840400</v>
+        <v>853100</v>
       </c>
       <c r="E27" s="3">
-        <v>1292500</v>
+        <v>1311900</v>
       </c>
       <c r="F27" s="3">
-        <v>808100</v>
+        <v>820300</v>
       </c>
       <c r="G27" s="3">
-        <v>-669600</v>
+        <v>-679700</v>
       </c>
       <c r="H27" s="3">
-        <v>-179200</v>
+        <v>-181900</v>
       </c>
       <c r="I27" s="3">
-        <v>716700</v>
+        <v>727500</v>
       </c>
       <c r="J27" s="3">
-        <v>1205300</v>
+        <v>1223400</v>
       </c>
       <c r="K27" s="3">
         <v>-4334700</v>
@@ -1537,19 +1537,19 @@
         <v>8</v>
       </c>
       <c r="F29" s="3">
-        <v>-51300</v>
+        <v>-52100</v>
       </c>
       <c r="G29" s="3">
-        <v>-91600</v>
+        <v>-93000</v>
       </c>
       <c r="H29" s="3">
-        <v>6907200</v>
+        <v>7011200</v>
       </c>
       <c r="I29" s="3">
-        <v>4621900</v>
+        <v>4691500</v>
       </c>
       <c r="J29" s="3">
-        <v>-7617300</v>
+        <v>-7732000</v>
       </c>
       <c r="K29" s="3">
         <v>953600</v>
@@ -1657,25 +1657,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-343800</v>
+        <v>-349000</v>
       </c>
       <c r="E32" s="3">
-        <v>-401100</v>
+        <v>-407100</v>
       </c>
       <c r="F32" s="3">
-        <v>-304500</v>
+        <v>-309100</v>
       </c>
       <c r="G32" s="3">
-        <v>955300</v>
+        <v>969700</v>
       </c>
       <c r="H32" s="3">
-        <v>-232600</v>
+        <v>-236100</v>
       </c>
       <c r="I32" s="3">
-        <v>-671800</v>
+        <v>-681900</v>
       </c>
       <c r="J32" s="3">
-        <v>-412000</v>
+        <v>-418200</v>
       </c>
       <c r="K32" s="3">
         <v>-746200</v>
@@ -1699,25 +1699,25 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>840400</v>
+        <v>853100</v>
       </c>
       <c r="E33" s="3">
-        <v>1292500</v>
+        <v>1311900</v>
       </c>
       <c r="F33" s="3">
-        <v>756800</v>
+        <v>768200</v>
       </c>
       <c r="G33" s="3">
-        <v>-761200</v>
+        <v>-772600</v>
       </c>
       <c r="H33" s="3">
-        <v>6728000</v>
+        <v>6829300</v>
       </c>
       <c r="I33" s="3">
-        <v>5338600</v>
+        <v>5419000</v>
       </c>
       <c r="J33" s="3">
-        <v>-6412000</v>
+        <v>-6508600</v>
       </c>
       <c r="K33" s="3">
         <v>-3381100</v>
@@ -1783,25 +1783,25 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>840400</v>
+        <v>853100</v>
       </c>
       <c r="E35" s="3">
-        <v>1292500</v>
+        <v>1311900</v>
       </c>
       <c r="F35" s="3">
-        <v>756800</v>
+        <v>768200</v>
       </c>
       <c r="G35" s="3">
-        <v>-761200</v>
+        <v>-772600</v>
       </c>
       <c r="H35" s="3">
-        <v>6728000</v>
+        <v>6829300</v>
       </c>
       <c r="I35" s="3">
-        <v>5338600</v>
+        <v>5419000</v>
       </c>
       <c r="J35" s="3">
-        <v>-6412000</v>
+        <v>-6508600</v>
       </c>
       <c r="K35" s="3">
         <v>-3381100</v>
@@ -1908,25 +1908,25 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>2169200</v>
+        <v>2201900</v>
       </c>
       <c r="E41" s="3">
-        <v>2796900</v>
+        <v>2839000</v>
       </c>
       <c r="F41" s="3">
-        <v>3489000</v>
+        <v>3541600</v>
       </c>
       <c r="G41" s="3">
-        <v>2503100</v>
+        <v>2540800</v>
       </c>
       <c r="H41" s="3">
-        <v>8867900</v>
+        <v>9001400</v>
       </c>
       <c r="I41" s="3">
-        <v>3325400</v>
+        <v>3375500</v>
       </c>
       <c r="J41" s="3">
-        <v>3460100</v>
+        <v>3512200</v>
       </c>
       <c r="K41" s="3">
         <v>7127400</v>
@@ -1992,25 +1992,25 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>6228500</v>
+        <v>6322300</v>
       </c>
       <c r="E43" s="3">
-        <v>6112700</v>
+        <v>6204700</v>
       </c>
       <c r="F43" s="3">
-        <v>6543700</v>
+        <v>6642300</v>
       </c>
       <c r="G43" s="3">
-        <v>6915300</v>
+        <v>7019400</v>
       </c>
       <c r="H43" s="3">
-        <v>7292000</v>
+        <v>7401900</v>
       </c>
       <c r="I43" s="3">
-        <v>7515500</v>
+        <v>7628700</v>
       </c>
       <c r="J43" s="3">
-        <v>7021700</v>
+        <v>7127500</v>
       </c>
       <c r="K43" s="3">
         <v>9314900</v>
@@ -2034,25 +2034,25 @@
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>3945200</v>
+        <v>4004600</v>
       </c>
       <c r="E44" s="3">
-        <v>3531100</v>
+        <v>3584300</v>
       </c>
       <c r="F44" s="3">
-        <v>3159100</v>
+        <v>3206700</v>
       </c>
       <c r="G44" s="3">
-        <v>3202700</v>
+        <v>3250900</v>
       </c>
       <c r="H44" s="3">
-        <v>3113300</v>
+        <v>3160200</v>
       </c>
       <c r="I44" s="3">
-        <v>3119300</v>
+        <v>3166200</v>
       </c>
       <c r="J44" s="3">
-        <v>3324600</v>
+        <v>3374600</v>
       </c>
       <c r="K44" s="3">
         <v>5359100</v>
@@ -2076,25 +2076,25 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>1347800</v>
+        <v>1368100</v>
       </c>
       <c r="E45" s="3">
-        <v>2605900</v>
+        <v>2645100</v>
       </c>
       <c r="F45" s="3">
-        <v>957400</v>
+        <v>971800</v>
       </c>
       <c r="G45" s="3">
-        <v>911900</v>
+        <v>925700</v>
       </c>
       <c r="H45" s="3">
-        <v>871600</v>
+        <v>884700</v>
       </c>
       <c r="I45" s="3">
-        <v>9805000</v>
+        <v>9952700</v>
       </c>
       <c r="J45" s="3">
-        <v>7371100</v>
+        <v>7482100</v>
       </c>
       <c r="K45" s="3">
         <v>3619200</v>
@@ -2118,25 +2118,25 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>13690800</v>
+        <v>13897000</v>
       </c>
       <c r="E46" s="3">
-        <v>15046500</v>
+        <v>15273100</v>
       </c>
       <c r="F46" s="3">
-        <v>14149200</v>
+        <v>14362300</v>
       </c>
       <c r="G46" s="3">
-        <v>13533000</v>
+        <v>13736800</v>
       </c>
       <c r="H46" s="3">
-        <v>20144800</v>
+        <v>20448200</v>
       </c>
       <c r="I46" s="3">
-        <v>23765200</v>
+        <v>24123100</v>
       </c>
       <c r="J46" s="3">
-        <v>21177400</v>
+        <v>21496400</v>
       </c>
       <c r="K46" s="3">
         <v>25420600</v>
@@ -2160,25 +2160,25 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>3560000</v>
+        <v>3613600</v>
       </c>
       <c r="E47" s="3">
-        <v>3742400</v>
+        <v>3798700</v>
       </c>
       <c r="F47" s="3">
-        <v>3545900</v>
+        <v>3599300</v>
       </c>
       <c r="G47" s="3">
-        <v>3404300</v>
+        <v>3455600</v>
       </c>
       <c r="H47" s="3">
-        <v>3954900</v>
+        <v>4014500</v>
       </c>
       <c r="I47" s="3">
-        <v>1632400</v>
+        <v>1657000</v>
       </c>
       <c r="J47" s="3">
-        <v>1499500</v>
+        <v>1522100</v>
       </c>
       <c r="K47" s="3">
         <v>2672100</v>
@@ -2202,25 +2202,25 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>3873900</v>
+        <v>3932300</v>
       </c>
       <c r="E48" s="3">
-        <v>3753900</v>
+        <v>3810500</v>
       </c>
       <c r="F48" s="3">
-        <v>3820900</v>
+        <v>3878500</v>
       </c>
       <c r="G48" s="3">
-        <v>3823400</v>
+        <v>3881000</v>
       </c>
       <c r="H48" s="3">
-        <v>2561200</v>
+        <v>2599800</v>
       </c>
       <c r="I48" s="3">
-        <v>2427800</v>
+        <v>2464400</v>
       </c>
       <c r="J48" s="3">
-        <v>2680800</v>
+        <v>2721200</v>
       </c>
       <c r="K48" s="3">
         <v>5838100</v>
@@ -2244,25 +2244,25 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>1046100</v>
+        <v>1061900</v>
       </c>
       <c r="E49" s="3">
-        <v>1051500</v>
+        <v>1067300</v>
       </c>
       <c r="F49" s="3">
-        <v>854900</v>
+        <v>867800</v>
       </c>
       <c r="G49" s="3">
-        <v>794700</v>
+        <v>806600</v>
       </c>
       <c r="H49" s="3">
-        <v>774200</v>
+        <v>785900</v>
       </c>
       <c r="I49" s="3">
-        <v>840000</v>
+        <v>852700</v>
       </c>
       <c r="J49" s="3">
-        <v>4697100</v>
+        <v>4767800</v>
       </c>
       <c r="K49" s="3">
         <v>4703200</v>
@@ -2370,25 +2370,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>1329900</v>
+        <v>1349900</v>
       </c>
       <c r="E52" s="3">
-        <v>1202900</v>
+        <v>1221000</v>
       </c>
       <c r="F52" s="3">
-        <v>873200</v>
+        <v>886300</v>
       </c>
       <c r="G52" s="3">
-        <v>910600</v>
+        <v>924400</v>
       </c>
       <c r="H52" s="3">
-        <v>1099300</v>
+        <v>1115800</v>
       </c>
       <c r="I52" s="3">
-        <v>937100</v>
+        <v>951200</v>
       </c>
       <c r="J52" s="3">
-        <v>695500</v>
+        <v>706000</v>
       </c>
       <c r="K52" s="3">
         <v>1301100</v>
@@ -2454,25 +2454,25 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>23500700</v>
+        <v>23854700</v>
       </c>
       <c r="E54" s="3">
-        <v>24797200</v>
+        <v>25170700</v>
       </c>
       <c r="F54" s="3">
-        <v>23244200</v>
+        <v>23594300</v>
       </c>
       <c r="G54" s="3">
-        <v>22466000</v>
+        <v>22804300</v>
       </c>
       <c r="H54" s="3">
-        <v>28534400</v>
+        <v>28964100</v>
       </c>
       <c r="I54" s="3">
-        <v>29602500</v>
+        <v>30048300</v>
       </c>
       <c r="J54" s="3">
-        <v>28349600</v>
+        <v>28776500</v>
       </c>
       <c r="K54" s="3">
         <v>39935100</v>
@@ -2532,25 +2532,25 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>4714200</v>
+        <v>4785200</v>
       </c>
       <c r="E57" s="3">
-        <v>5028000</v>
+        <v>5103700</v>
       </c>
       <c r="F57" s="3">
-        <v>4859300</v>
+        <v>4932500</v>
       </c>
       <c r="G57" s="3">
-        <v>5232800</v>
+        <v>5311600</v>
       </c>
       <c r="H57" s="3">
-        <v>6362000</v>
+        <v>6457800</v>
       </c>
       <c r="I57" s="3">
-        <v>6562000</v>
+        <v>6660800</v>
       </c>
       <c r="J57" s="3">
-        <v>6247700</v>
+        <v>6341800</v>
       </c>
       <c r="K57" s="3">
         <v>10268600</v>
@@ -2574,25 +2574,25 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>398100</v>
+        <v>404100</v>
       </c>
       <c r="E58" s="3">
-        <v>502500</v>
+        <v>510100</v>
       </c>
       <c r="F58" s="3">
-        <v>106200</v>
+        <v>107800</v>
       </c>
       <c r="G58" s="3">
-        <v>416000</v>
+        <v>422300</v>
       </c>
       <c r="H58" s="3">
-        <v>2375400</v>
+        <v>2411200</v>
       </c>
       <c r="I58" s="3">
-        <v>2002300</v>
+        <v>2032500</v>
       </c>
       <c r="J58" s="3">
-        <v>6732100</v>
+        <v>6833500</v>
       </c>
       <c r="K58" s="3">
         <v>4554100</v>
@@ -2616,25 +2616,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>3976800</v>
+        <v>4036700</v>
       </c>
       <c r="E59" s="3">
-        <v>4495000</v>
+        <v>4562700</v>
       </c>
       <c r="F59" s="3">
-        <v>3367000</v>
+        <v>3417700</v>
       </c>
       <c r="G59" s="3">
-        <v>3633400</v>
+        <v>3688100</v>
       </c>
       <c r="H59" s="3">
-        <v>3735300</v>
+        <v>3791600</v>
       </c>
       <c r="I59" s="3">
-        <v>7577100</v>
+        <v>7691200</v>
       </c>
       <c r="J59" s="3">
-        <v>7689200</v>
+        <v>7805000</v>
       </c>
       <c r="K59" s="3">
         <v>7756500</v>
@@ -2658,25 +2658,25 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>9089100</v>
+        <v>9226000</v>
       </c>
       <c r="E60" s="3">
-        <v>10025500</v>
+        <v>10176500</v>
       </c>
       <c r="F60" s="3">
-        <v>8332400</v>
+        <v>8457900</v>
       </c>
       <c r="G60" s="3">
-        <v>9282200</v>
+        <v>9422000</v>
       </c>
       <c r="H60" s="3">
-        <v>12472700</v>
+        <v>12660500</v>
       </c>
       <c r="I60" s="3">
-        <v>16141400</v>
+        <v>16384500</v>
       </c>
       <c r="J60" s="3">
-        <v>18490600</v>
+        <v>18769100</v>
       </c>
       <c r="K60" s="3">
         <v>22579300</v>
@@ -2700,25 +2700,25 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>2207300</v>
+        <v>2240500</v>
       </c>
       <c r="E61" s="3">
-        <v>2109300</v>
+        <v>2141000</v>
       </c>
       <c r="F61" s="3">
-        <v>2512800</v>
+        <v>2550700</v>
       </c>
       <c r="G61" s="3">
-        <v>1153700</v>
+        <v>1171100</v>
       </c>
       <c r="H61" s="3">
-        <v>510800</v>
+        <v>518500</v>
       </c>
       <c r="I61" s="3">
-        <v>2595300</v>
+        <v>2634400</v>
       </c>
       <c r="J61" s="3">
-        <v>3440700</v>
+        <v>3492500</v>
       </c>
       <c r="K61" s="3">
         <v>6110100</v>
@@ -2742,25 +2742,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>3326300</v>
+        <v>3376400</v>
       </c>
       <c r="E62" s="3">
-        <v>3587800</v>
+        <v>3641800</v>
       </c>
       <c r="F62" s="3">
-        <v>3736900</v>
+        <v>3793200</v>
       </c>
       <c r="G62" s="3">
-        <v>4882600</v>
+        <v>4956200</v>
       </c>
       <c r="H62" s="3">
-        <v>4269200</v>
+        <v>4333400</v>
       </c>
       <c r="I62" s="3">
-        <v>4154500</v>
+        <v>4217100</v>
       </c>
       <c r="J62" s="3">
-        <v>8249000</v>
+        <v>8373200</v>
       </c>
       <c r="K62" s="3">
         <v>6304600</v>
@@ -2910,25 +2910,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>15218100</v>
+        <v>15447300</v>
       </c>
       <c r="E66" s="3">
-        <v>16785200</v>
+        <v>17037900</v>
       </c>
       <c r="F66" s="3">
-        <v>15511700</v>
+        <v>15745300</v>
       </c>
       <c r="G66" s="3">
-        <v>16225700</v>
+        <v>16470000</v>
       </c>
       <c r="H66" s="3">
-        <v>18862100</v>
+        <v>19146200</v>
       </c>
       <c r="I66" s="3">
-        <v>24402500</v>
+        <v>24770000</v>
       </c>
       <c r="J66" s="3">
-        <v>32021100</v>
+        <v>32503400</v>
       </c>
       <c r="K66" s="3">
         <v>37517800</v>
@@ -3138,25 +3138,25 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>7428600</v>
+        <v>7540500</v>
       </c>
       <c r="E72" s="3">
-        <v>7423800</v>
+        <v>7535600</v>
       </c>
       <c r="F72" s="3">
-        <v>7484100</v>
+        <v>7596900</v>
       </c>
       <c r="G72" s="3">
-        <v>6847400</v>
+        <v>6950500</v>
       </c>
       <c r="H72" s="3">
-        <v>10149000</v>
+        <v>10301800</v>
       </c>
       <c r="I72" s="3">
-        <v>1484800</v>
+        <v>1507200</v>
       </c>
       <c r="J72" s="3">
-        <v>-3853800</v>
+        <v>-3911900</v>
       </c>
       <c r="K72" s="3">
         <v>-564300</v>
@@ -3306,25 +3306,25 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>8282600</v>
+        <v>8407300</v>
       </c>
       <c r="E76" s="3">
-        <v>8012000</v>
+        <v>8132700</v>
       </c>
       <c r="F76" s="3">
-        <v>7732500</v>
+        <v>7849000</v>
       </c>
       <c r="G76" s="3">
-        <v>6240300</v>
+        <v>6334300</v>
       </c>
       <c r="H76" s="3">
-        <v>9672200</v>
+        <v>9817900</v>
       </c>
       <c r="I76" s="3">
-        <v>5200000</v>
+        <v>5278300</v>
       </c>
       <c r="J76" s="3">
-        <v>-3671600</v>
+        <v>-3726900</v>
       </c>
       <c r="K76" s="3">
         <v>2417200</v>
@@ -3437,25 +3437,25 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>840400</v>
+        <v>853100</v>
       </c>
       <c r="E81" s="3">
-        <v>1292500</v>
+        <v>1311900</v>
       </c>
       <c r="F81" s="3">
-        <v>756800</v>
+        <v>768200</v>
       </c>
       <c r="G81" s="3">
-        <v>-761200</v>
+        <v>-772600</v>
       </c>
       <c r="H81" s="3">
-        <v>6728000</v>
+        <v>6829300</v>
       </c>
       <c r="I81" s="3">
-        <v>5338600</v>
+        <v>5419000</v>
       </c>
       <c r="J81" s="3">
-        <v>-6412000</v>
+        <v>-6508600</v>
       </c>
       <c r="K81" s="3">
         <v>-3381100</v>
@@ -3497,25 +3497,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>633000</v>
+        <v>642500</v>
       </c>
       <c r="E83" s="3">
-        <v>565400</v>
+        <v>574000</v>
       </c>
       <c r="F83" s="3">
-        <v>565800</v>
+        <v>574300</v>
       </c>
       <c r="G83" s="3">
-        <v>528600</v>
+        <v>536600</v>
       </c>
       <c r="H83" s="3">
-        <v>521400</v>
+        <v>529200</v>
       </c>
       <c r="I83" s="3">
-        <v>784000</v>
+        <v>795800</v>
       </c>
       <c r="J83" s="3">
-        <v>1082200</v>
+        <v>1098500</v>
       </c>
       <c r="K83" s="3">
         <v>1571900</v>
@@ -3749,25 +3749,25 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>226000</v>
+        <v>229400</v>
       </c>
       <c r="E89" s="3">
-        <v>1511000</v>
+        <v>1533800</v>
       </c>
       <c r="F89" s="3">
-        <v>963800</v>
+        <v>978300</v>
       </c>
       <c r="G89" s="3">
-        <v>-943900</v>
+        <v>-958100</v>
       </c>
       <c r="H89" s="3">
-        <v>829000</v>
+        <v>841500</v>
       </c>
       <c r="I89" s="3">
-        <v>248100</v>
+        <v>251900</v>
       </c>
       <c r="J89" s="3">
-        <v>890800</v>
+        <v>904300</v>
       </c>
       <c r="K89" s="3">
         <v>-9000</v>
@@ -3809,25 +3809,25 @@
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-788000</v>
+        <v>-799900</v>
       </c>
       <c r="E91" s="3">
-        <v>-629300</v>
+        <v>-638800</v>
       </c>
       <c r="F91" s="3">
-        <v>-779900</v>
+        <v>-791700</v>
       </c>
       <c r="G91" s="3">
-        <v>-791900</v>
+        <v>-803900</v>
       </c>
       <c r="H91" s="3">
-        <v>-813800</v>
+        <v>-826000</v>
       </c>
       <c r="I91" s="3">
-        <v>-1188700</v>
+        <v>-1206600</v>
       </c>
       <c r="J91" s="3">
-        <v>-1054100</v>
+        <v>-1070000</v>
       </c>
       <c r="K91" s="3">
         <v>-1778800</v>
@@ -3935,25 +3935,25 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-58500</v>
+        <v>-59400</v>
       </c>
       <c r="E94" s="3">
-        <v>-826800</v>
+        <v>-839300</v>
       </c>
       <c r="F94" s="3">
-        <v>-708300</v>
+        <v>-719000</v>
       </c>
       <c r="G94" s="3">
-        <v>-813500</v>
+        <v>-825700</v>
       </c>
       <c r="H94" s="3">
-        <v>8668100</v>
+        <v>8798600</v>
       </c>
       <c r="I94" s="3">
-        <v>-974200</v>
+        <v>-988800</v>
       </c>
       <c r="J94" s="3">
-        <v>-1188100</v>
+        <v>-1206000</v>
       </c>
       <c r="K94" s="3">
         <v>4802800</v>
@@ -3995,25 +3995,25 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-894900</v>
+        <v>-908400</v>
       </c>
       <c r="E96" s="3">
-        <v>-726600</v>
+        <v>-737600</v>
       </c>
       <c r="F96" s="3">
-        <v>-141400</v>
+        <v>-143500</v>
       </c>
       <c r="G96" s="3">
-        <v>-154800</v>
+        <v>-157200</v>
       </c>
       <c r="H96" s="3">
-        <v>-147700</v>
+        <v>-150000</v>
       </c>
       <c r="I96" s="3">
-        <v>-72600</v>
+        <v>-73700</v>
       </c>
       <c r="J96" s="3">
-        <v>-84700</v>
+        <v>-86000</v>
       </c>
       <c r="K96" s="3">
         <v>-234100</v>
@@ -4163,25 +4163,25 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-945200</v>
+        <v>-959400</v>
       </c>
       <c r="E100" s="3">
-        <v>-1439800</v>
+        <v>-1461400</v>
       </c>
       <c r="F100" s="3">
-        <v>649500</v>
+        <v>659200</v>
       </c>
       <c r="G100" s="3">
-        <v>-4563300</v>
+        <v>-4632000</v>
       </c>
       <c r="H100" s="3">
-        <v>-4282900</v>
+        <v>-4347400</v>
       </c>
       <c r="I100" s="3">
-        <v>-422400</v>
+        <v>-428800</v>
       </c>
       <c r="J100" s="3">
-        <v>-1459200</v>
+        <v>-1481200</v>
       </c>
       <c r="K100" s="3">
         <v>997700</v>
@@ -4205,25 +4205,25 @@
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>6000</v>
+        <v>6100</v>
       </c>
       <c r="E101" s="3">
-        <v>63400</v>
+        <v>64400</v>
       </c>
       <c r="F101" s="3">
-        <v>81000</v>
+        <v>82200</v>
       </c>
       <c r="G101" s="3">
-        <v>-44100</v>
+        <v>-44800</v>
       </c>
       <c r="H101" s="3">
-        <v>10600</v>
+        <v>10700</v>
       </c>
       <c r="I101" s="3">
-        <v>-10700</v>
+        <v>-10900</v>
       </c>
       <c r="J101" s="3">
-        <v>-22000</v>
+        <v>-22300</v>
       </c>
       <c r="K101" s="3">
         <v>-86700</v>
@@ -4247,25 +4247,25 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-771600</v>
+        <v>-783200</v>
       </c>
       <c r="E102" s="3">
-        <v>-692100</v>
+        <v>-702600</v>
       </c>
       <c r="F102" s="3">
-        <v>985900</v>
+        <v>1000800</v>
       </c>
       <c r="G102" s="3">
-        <v>-6364800</v>
+        <v>-6460600</v>
       </c>
       <c r="H102" s="3">
-        <v>5224800</v>
+        <v>5303500</v>
       </c>
       <c r="I102" s="3">
-        <v>-1159200</v>
+        <v>-1176600</v>
       </c>
       <c r="J102" s="3">
-        <v>-1778400</v>
+        <v>-1805200</v>
       </c>
       <c r="K102" s="3">
         <v>5704800</v>
